--- a/data/trans_bre/P6902-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6902-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 19,25</t>
+          <t>-16,32; 17,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 37,07</t>
+          <t>-4,09; 36,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 11,33</t>
+          <t>-35,6; 12,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 21,02</t>
+          <t>-35,85; 22,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,92; 91,0</t>
+          <t>-52,7; 85,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 149,24</t>
+          <t>-10,99; 138,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-78,18; 35,02</t>
+          <t>-75,96; 38,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-61,28; 50,45</t>
+          <t>-58,09; 60,42</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 18,34</t>
+          <t>-3,37; 18,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 19,08</t>
+          <t>-2,4; 19,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,1; 33,07</t>
+          <t>11,95; 33,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 7,31</t>
+          <t>-24,84; 8,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 47,52</t>
+          <t>-7,17; 51,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 46,18</t>
+          <t>-4,63; 48,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,47; 105,73</t>
+          <t>30,79; 106,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,14; 13,48</t>
+          <t>-41,36; 15,38</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 7,89</t>
+          <t>-21,88; 7,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 20,17</t>
+          <t>-19,06; 19,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 20,06</t>
+          <t>-14,44; 19,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 12,61</t>
+          <t>-8,29; 12,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 11,17</t>
+          <t>-26,64; 10,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 32,08</t>
+          <t>-23,58; 31,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 35,38</t>
+          <t>-18,21; 32,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 16,26</t>
+          <t>-8,81; 15,38</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 17,13</t>
+          <t>-0,27; 15,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 18,81</t>
+          <t>1,16; 19,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 25,25</t>
+          <t>8,73; 26,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 8,15</t>
+          <t>-17,7; 8,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 43,04</t>
+          <t>-0,43; 39,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 44,15</t>
+          <t>1,89; 44,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,24; 63,37</t>
+          <t>19,19; 68,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 13,85</t>
+          <t>-29,12; 13,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6902-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6902-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,94</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-9,81%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 17,32</t>
+          <t>-15,85; 18,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 36,76</t>
+          <t>-4,56; 36,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 12,66</t>
+          <t>-34,36; 14,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,85; 22,75</t>
+          <t>-21,08; 23,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,7; 85,36</t>
+          <t>-54,64; 91,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 138,86</t>
+          <t>-10,66; 145,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-75,96; 38,35</t>
+          <t>-74,2; 39,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,09; 60,42</t>
+          <t>-33,04; 70,19</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,98</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,13%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 18,76</t>
+          <t>-4,29; 18,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 19,48</t>
+          <t>-2,01; 20,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,95; 33,54</t>
+          <t>11,73; 32,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 8,07</t>
+          <t>-3,34; 14,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 51,63</t>
+          <t>-8,91; 49,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 48,33</t>
+          <t>-4,08; 49,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,79; 106,77</t>
+          <t>28,19; 101,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 15,38</t>
+          <t>-5,57; 28,89</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>-1,12%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 7,33</t>
+          <t>-23,96; 7,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 19,86</t>
+          <t>-21,73; 19,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 19,19</t>
+          <t>-13,14; 20,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 12,15</t>
+          <t>-9,85; 10,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 10,32</t>
+          <t>-28,52; 9,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 31,68</t>
+          <t>-28,11; 31,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 32,99</t>
+          <t>-16,96; 35,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 15,38</t>
+          <t>-10,63; 12,63</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-1,91%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 15,65</t>
+          <t>-0,25; 15,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 19,1</t>
+          <t>1,11; 19,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 26,35</t>
+          <t>8,59; 25,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 8,38</t>
+          <t>-1,09; 13,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 39,4</t>
+          <t>-0,4; 39,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 44,18</t>
+          <t>2,61; 45,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,19; 68,91</t>
+          <t>19,39; 67,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 13,89</t>
+          <t>-1,58; 23,09</t>
         </is>
       </c>
     </row>
